--- a/data/trans_orig/IP3109_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Habitat-trans_orig.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137319</t>
+          <t>137889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266708</t>
+          <t>266731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172468</t>
+          <t>172480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198059</t>
+          <t>197723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372857</t>
+          <t>373177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121598</t>
+          <t>122141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126585</t>
+          <t>126579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131374</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256055</t>
+          <t>255767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261115</t>
+          <t>261109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192269</t>
+          <t>192285</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190588</t>
+          <t>190587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385018</t>
+          <t>385643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>621017</t>
+          <t>621727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>628319</t>
+          <t>628439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>664625</t>
+          <t>665100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>670309</t>
+          <t>670356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,42 +2155,42 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1294077</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1288427</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1297908</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>98,97%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1294077</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1289399</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1297914</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3947</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>13428</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126024</t>
+          <t>125937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134961</t>
+          <t>135014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263837</t>
+          <t>264269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269537</t>
+          <t>269543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181684</t>
+          <t>181883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>188724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198015</t>
+          <t>198038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383160</t>
+          <t>382823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390490</t>
+          <t>390638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132049</t>
+          <t>132248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138326</t>
+          <t>138324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146070</t>
+          <t>146006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280280</t>
+          <t>280853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286848</t>
+          <t>286888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180346</t>
+          <t>180157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186745</t>
+          <t>186739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185182</t>
+          <t>184369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369640</t>
+          <t>368913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>377491</t>
+          <t>377365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>630524</t>
+          <t>630783</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>640821</t>
+          <t>641741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>672531</t>
+          <t>673390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>681309</t>
+          <t>681379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1307020</t>
+          <t>1307067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1320376</t>
+          <t>1320709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114849</t>
+          <t>114739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249225</t>
+          <t>249200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183657</t>
+          <t>183356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189647</t>
+          <t>189640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201047</t>
+          <t>200614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386646</t>
+          <t>386931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393439</t>
+          <t>393499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134872</t>
+          <t>135851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150965</t>
+          <t>151496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288656</t>
+          <t>288684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292981</t>
+          <t>292976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>181581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187450</t>
+          <t>187636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>180548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185859</t>
+          <t>185850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365154</t>
+          <t>365355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372773</t>
+          <t>372748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>623967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>633248</t>
+          <t>633158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>671670</t>
+          <t>671595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>678192</t>
+          <t>678189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1298837</t>
+          <t>1298866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1310327</t>
+          <t>1310047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89671</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101944</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106945</t>
+          <t>106576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122491</t>
+          <t>121985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200092</t>
+          <t>200984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221333</t>
+          <t>220549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148830</t>
+          <t>147894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165575</t>
+          <t>165008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196726</t>
+          <t>197024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218670</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>352203</t>
+          <t>352617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379976</t>
+          <t>380317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50794</t>
+          <t>50496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81431</t>
+          <t>81017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152791</t>
+          <t>153167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173012</t>
+          <t>173793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145589</t>
+          <t>144895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164036</t>
+          <t>163351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305490</t>
+          <t>306073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>333434</t>
+          <t>335319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>65266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136515</t>
+          <t>137200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150893</t>
+          <t>151276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142001</t>
+          <t>142768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158090</t>
+          <t>158369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>283449</t>
+          <t>284014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305418</t>
+          <t>305621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>34541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58379</t>
+          <t>57814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546448</t>
+          <t>546713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>578200</t>
+          <t>578076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>610647</t>
+          <t>612287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648538</t>
+          <t>648671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1167812</t>
+          <t>1170793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1216947</t>
+          <t>1216566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>74233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105861</t>
+          <t>105596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95631</t>
+          <t>95498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>131882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179531</t>
+          <t>179912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228666</t>
+          <t>225685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>140342</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>137332</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>141537</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>128813</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>137889</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>141537</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>396</t>
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266731</t>
+          <t>266173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1195</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4177</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>128813</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>128813</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>128813</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,74 +1066,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>200838</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>198039</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>201536</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>175708</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>172480</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>172461</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>177004</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>200838</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>197723</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>201536</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>586</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373177</t>
+          <t>372631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377899</t>
+          <t>377900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4524</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>201536</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>201536</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>201536</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>177004</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>177004</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>177004</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>201536</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>201536</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>201536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133989</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>131366</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>134637</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>125267</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>122141</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>126579</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>120726</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>126582</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>98,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>133989</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>131095</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>134637</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255767</t>
+          <t>255460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261109</t>
+          <t>261111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1848</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6389</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3542</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>134637</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>134637</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>134637</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127115</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127115</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127115</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>134637</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>134637</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>134637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,74 +1752,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>193196</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>189926</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>193845</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>195924</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>192285</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>193008</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>197368</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>193196</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>190587</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>193845</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>540</t>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385643</t>
+          <t>385305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3919</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1444</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>193845</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>193845</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>193845</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>197368</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>197368</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>197368</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>193845</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>193845</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>193845</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>668364</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>663978</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>670307</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>625712</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>621727</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>628439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>621572</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>628395</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>668364</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>665100</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>670356</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1937</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1288427</t>
+          <t>1288767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1297908</t>
+          <t>1297479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4588</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8573</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8728</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6454</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,74 +2670,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>138679</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>135042</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>140146</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>129342</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>125937</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>126459</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>130078</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>138679</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>135014</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>140146</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>365</t>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264269</t>
+          <t>263179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>269534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5104</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>140146</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>140146</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>140146</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130078</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130078</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130078</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>140146</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>140146</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>140146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>201406</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>198110</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>202725</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>186208</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>181883</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>188724</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>181848</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>188649</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>97,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>201406</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>198038</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>202725</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>382823</t>
+          <t>383418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390638</t>
+          <t>390689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4271</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8596</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8631</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3244,52 +3244,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>202725</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>202725</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>202725</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>190479</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>190479</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>190479</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>202725</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>202725</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>202725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148502</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>146035</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149109</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136297</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132248</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>138324</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>132238</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>138332</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>98,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148502</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>146006</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>149109</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280853</t>
+          <t>280579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286888</t>
+          <t>286827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3074</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6798</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6808</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149109</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149109</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149109</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>139046</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>139046</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>139046</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149109</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149109</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,74 +3699,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>189625</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>185210</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>191376</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>184875</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>180157</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>180025</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>186739</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>98,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>189625</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>184369</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>191376</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>499</t>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368913</t>
+          <t>368605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>377365</t>
+          <t>377489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2611</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7329</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7007</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>191376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>191376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187486</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187486</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187486</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>191376</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191376</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>191376</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>678211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>672601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>681256</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>636722</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>630783</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>641741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>630203</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>641399</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>678211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>673390</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>681379</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1307067</t>
+          <t>1307488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1320709</t>
+          <t>1320651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10754</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>10367</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16306</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5690</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16886</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9965</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,74 +4617,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>134483</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>118162</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>114739</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>114673</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>119525</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>98,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>134483</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>341</t>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249200</t>
+          <t>249463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4545</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4808</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>134483</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>134483</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>134483</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>119525</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>119525</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>119525</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>134483</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>134483</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>134483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>203682</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>200810</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>204397</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>187362</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>183356</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>189640</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>183235</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>189250</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>203682</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>200614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>204397</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386931</t>
+          <t>386924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393499</t>
+          <t>393590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3553</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7559</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1665</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7680</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3783</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204397</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204397</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204397</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>190915</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>190915</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>190915</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204397</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204397</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204397</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,74 +5303,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153456</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>150984</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>154082</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>138280</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>135851</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>135352</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>139435</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>153456</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>151496</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>154082</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288684</t>
+          <t>288798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292976</t>
+          <t>292979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1155</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2586</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>154082</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>154082</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>154082</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>139435</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>139435</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>139435</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>154082</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>154082</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>154082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>184395</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>180779</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185851</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>185526</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>181581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>187636</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>181756</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>187444</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>184395</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>180548</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>185850</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365355</t>
+          <t>364199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372748</t>
+          <t>372641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5781</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6694</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6519</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6012</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186560</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186560</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186560</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188275</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188275</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188275</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186560</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186560</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186560</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>676016</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>671818</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>678182</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>629330</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>623967</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>633158</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>623491</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>633072</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>676016</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>671595</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>678189</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1298866</t>
+          <t>1298718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1310047</t>
+          <t>1309896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>8820</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7927</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103480</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95854</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>108944</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>96308</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89695</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101474</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>115154</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106576</t>
+          <t>92605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>105917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>211463</t>
+          <t>203752</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200984</t>
+          <t>193825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220549</t>
+          <t>212725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18904</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13440</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26530</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17118</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11952</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23731</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29674</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136250</t>
+          <t>117724</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136250</t>
+          <t>117724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136250</t>
+          <t>117724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>198602</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>188794</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>207234</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>157759</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>147894</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>165008</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,76%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>208985</t>
+          <t>152885</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>197024</t>
+          <t>143348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218906</t>
+          <t>160479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>366743</t>
+          <t>351486</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>352617</t>
+          <t>337448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380317</t>
+          <t>362623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32639</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24007</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42447</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28355</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21106</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38220</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28614</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50496</t>
+          <t>37245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>66891</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53317</t>
+          <t>49210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81017</t>
+          <t>74385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143295</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>133336</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149820</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>163688</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>153167</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>173793</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>130707</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144895</t>
+          <t>122386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163351</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>319758</t>
+          <t>274002</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306073</t>
+          <t>262744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>335319</t>
+          <t>284173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23227</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16702</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33186</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24561</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14456</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35082</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>51581</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65266</t>
+          <t>58816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141773</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>133611</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>148398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>144933</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>137200</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>151276</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>83,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>150968</t>
+          <t>143634</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142768</t>
+          <t>135765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158369</t>
+          <t>149744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>295901</t>
+          <t>285407</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284014</t>
+          <t>274835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305621</t>
+          <t>294981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24392</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17767</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32554</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19586</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27319</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57814</t>
+          <t>55309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>587149</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>573183</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>602201</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>779</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>562689</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>546713</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>578076</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>631176</t>
+          <t>527499</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>612287</t>
+          <t>510168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648671</t>
+          <t>540931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1193865</t>
+          <t>1114648</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1170793</t>
+          <t>1091553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1216566</t>
+          <t>1133237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>99163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113129</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>89620</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>74233</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>105596</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131882</t>
+          <t>107166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>202613</t>
+          <t>188998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179912</t>
+          <t>170409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225685</t>
+          <t>212093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
